--- a/artfynd/A 61824-2025 artfynd.xlsx
+++ b/artfynd/A 61824-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130243809</v>
       </c>
       <c r="B2" t="n">
-        <v>91814</v>
+        <v>91901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130244132</v>
       </c>
       <c r="B3" t="n">
-        <v>91652</v>
+        <v>91739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130244332</v>
       </c>
       <c r="B4" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130244182</v>
       </c>
       <c r="B5" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>130243363</v>
       </c>
       <c r="B6" t="n">
-        <v>96059</v>
+        <v>96146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>130244467</v>
       </c>
       <c r="B7" t="n">
-        <v>96059</v>
+        <v>96146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>130244293</v>
       </c>
       <c r="B10" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>130243835</v>
       </c>
       <c r="B11" t="n">
-        <v>79127</v>
+        <v>79212</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>130244448</v>
       </c>
       <c r="B12" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,6 +1758,1889 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130257365</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91728</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>621650</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6896202</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130255559</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96146</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>621737</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6896220</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130255573</v>
+      </c>
+      <c r="B15" t="n">
+        <v>105987</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>621738</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6896216</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130256102</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91692</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>621647</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6896273</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130263830</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57007</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Njurunda, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>621662</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6896601</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130256142</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90760</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>621632</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6896320</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130257248</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91728</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>621616</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6896252</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130255731</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80245</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>621752</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6896206</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130255442</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91728</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>621778</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6896212</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130255089</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57985</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>621974</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6896153</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130255474</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>621778</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6896212</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130255326</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79212</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>185</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>621779</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6896211</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130255188</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79212</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>185</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>621820</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6896258</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130256107</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91742</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>621653</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6896262</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130255328</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>621778</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6896212</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130256265</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79799</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>621538</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6896297</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130255532</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91692</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>621763</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6896229</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130257300</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91692</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>621622</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6896214</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130255293</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>621791</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6896209</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61824-2025 artfynd.xlsx
+++ b/artfynd/A 61824-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130243809</v>
+        <v>130243835</v>
       </c>
       <c r="B2" t="n">
-        <v>91934</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621527</v>
+        <v>621536</v>
       </c>
       <c r="R2" t="n">
-        <v>6896581</v>
+        <v>6896570</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Under gammal silverlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130244132</v>
+        <v>130255188</v>
       </c>
       <c r="B3" t="n">
-        <v>91772</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621616</v>
+        <v>621820</v>
       </c>
       <c r="R3" t="n">
-        <v>6896660</v>
+        <v>6896258</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -842,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130244332</v>
+        <v>130255326</v>
       </c>
       <c r="B4" t="n">
-        <v>92059</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621595</v>
+        <v>621779</v>
       </c>
       <c r="R4" t="n">
-        <v>6896653</v>
+        <v>6896211</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -939,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,54 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130243363</v>
+        <v>130244332</v>
       </c>
       <c r="B5" t="n">
-        <v>96183</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargberget, Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621643</v>
+        <v>621595</v>
       </c>
       <c r="R5" t="n">
-        <v>6896671</v>
+        <v>6896653</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1080,7 +1066,7 @@
         <v>130244182</v>
       </c>
       <c r="B6" t="n">
-        <v>91761</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130244467</v>
+        <v>130244293</v>
       </c>
       <c r="B7" t="n">
-        <v>96183</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621601</v>
+        <v>621607</v>
       </c>
       <c r="R7" t="n">
-        <v>6896657</v>
+        <v>6896640</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1271,50 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130243698</v>
+        <v>130244448</v>
       </c>
       <c r="B8" t="n">
-        <v>5177</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargberget, Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>621551</v>
+        <v>621601</v>
       </c>
       <c r="R8" t="n">
-        <v>6896636</v>
+        <v>6896657</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1373,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130243894</v>
+        <v>130255442</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621536</v>
+        <v>621778</v>
       </c>
       <c r="R9" t="n">
-        <v>6896570</v>
+        <v>6896212</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1438,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1470,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130244293</v>
+        <v>130257248</v>
       </c>
       <c r="B10" t="n">
-        <v>91761</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621607</v>
+        <v>621616</v>
       </c>
       <c r="R10" t="n">
-        <v>6896640</v>
+        <v>6896252</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1535,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1567,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130243835</v>
+        <v>130257365</v>
       </c>
       <c r="B11" t="n">
-        <v>79243</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1578,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621536</v>
+        <v>621650</v>
       </c>
       <c r="R11" t="n">
-        <v>6896570</v>
+        <v>6896202</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1632,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1664,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130244448</v>
+        <v>130256107</v>
       </c>
       <c r="B12" t="n">
-        <v>91761</v>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621601</v>
+        <v>621653</v>
       </c>
       <c r="R12" t="n">
-        <v>6896657</v>
+        <v>6896262</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1729,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1761,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130257365</v>
+        <v>130244132</v>
       </c>
       <c r="B13" t="n">
-        <v>91774</v>
+        <v>91920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621650</v>
+        <v>621616</v>
       </c>
       <c r="R13" t="n">
-        <v>6896202</v>
+        <v>6896660</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1826,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1858,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130255559</v>
+        <v>130243809</v>
       </c>
       <c r="B14" t="n">
-        <v>96196</v>
+        <v>92083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621737</v>
+        <v>621527</v>
       </c>
       <c r="R14" t="n">
-        <v>6896220</v>
+        <v>6896581</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1923,12 +1904,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Under gammal silverlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1955,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130255573</v>
+        <v>130256142</v>
       </c>
       <c r="B15" t="n">
-        <v>106037</v>
+        <v>90932</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621738</v>
+        <v>621632</v>
       </c>
       <c r="R15" t="n">
-        <v>6896216</v>
+        <v>6896320</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2052,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130256102</v>
+        <v>130243363</v>
       </c>
       <c r="B16" t="n">
-        <v>91737</v>
+        <v>96338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2063,34 +2049,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vargberget, Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621647</v>
+        <v>621643</v>
       </c>
       <c r="R16" t="n">
-        <v>6896273</v>
+        <v>6896671</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2117,12 +2112,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2149,60 +2144,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130263830</v>
+        <v>130244467</v>
       </c>
       <c r="B17" t="n">
-        <v>57043</v>
+        <v>96338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>2809</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vargberget, Vargberget, Njurunda, Mpd</t>
+          <t>Vargberget, Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>621662</v>
+        <v>621601</v>
       </c>
       <c r="R17" t="n">
-        <v>6896601</v>
+        <v>6896657</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2258,32 +2241,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130256142</v>
+        <v>130255559</v>
       </c>
       <c r="B18" t="n">
-        <v>90805</v>
+        <v>96338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1962</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621632</v>
+        <v>621737</v>
       </c>
       <c r="R18" t="n">
-        <v>6896320</v>
+        <v>6896220</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2355,32 +2338,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130257248</v>
+        <v>130255532</v>
       </c>
       <c r="B19" t="n">
-        <v>91774</v>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2390,13 +2373,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621616</v>
+        <v>621763</v>
       </c>
       <c r="R19" t="n">
-        <v>6896252</v>
+        <v>6896229</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2452,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130255731</v>
+        <v>130256102</v>
       </c>
       <c r="B20" t="n">
-        <v>80284</v>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2463,21 +2446,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2487,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>621752</v>
+        <v>621647</v>
       </c>
       <c r="R20" t="n">
-        <v>6896206</v>
+        <v>6896273</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2549,32 +2532,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130255442</v>
+        <v>130257300</v>
       </c>
       <c r="B21" t="n">
-        <v>91774</v>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2584,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>621778</v>
+        <v>621622</v>
       </c>
       <c r="R21" t="n">
-        <v>6896212</v>
+        <v>6896214</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2646,38 +2629,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130255474</v>
+        <v>130255293</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2686,10 +2673,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>621778</v>
+        <v>621791</v>
       </c>
       <c r="R22" t="n">
-        <v>6896212</v>
+        <v>6896209</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2748,10 +2735,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130255089</v>
+        <v>130256265</v>
       </c>
       <c r="B23" t="n">
-        <v>58021</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2759,46 +2746,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
+          <t>Vargberget, Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>621974</v>
+        <v>621538</v>
       </c>
       <c r="R23" t="n">
-        <v>6896153</v>
+        <v>6896297</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2854,32 +2832,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130255326</v>
+        <v>130256808</v>
       </c>
       <c r="B24" t="n">
-        <v>79251</v>
+        <v>80336</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2867,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>621779</v>
+        <v>621547</v>
       </c>
       <c r="R24" t="n">
-        <v>6896211</v>
+        <v>6896183</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2951,10 +2929,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130255188</v>
+        <v>130263778</v>
       </c>
       <c r="B25" t="n">
-        <v>79251</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,37 +2940,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vargberget, Vargberget, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>621820</v>
+        <v>621592</v>
       </c>
       <c r="R25" t="n">
-        <v>6896258</v>
+        <v>6896635</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3016,12 +2999,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3048,10 +3031,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130256107</v>
+        <v>130263780</v>
       </c>
       <c r="B26" t="n">
-        <v>91788</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3059,37 +3042,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vargberget, Vargberget, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>621653</v>
+        <v>621666</v>
       </c>
       <c r="R26" t="n">
-        <v>6896262</v>
+        <v>6896644</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3113,12 +3101,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3145,10 +3133,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130256265</v>
+        <v>130263781</v>
       </c>
       <c r="B27" t="n">
-        <v>79838</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3156,37 +3144,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vargberget, Vargberget, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>621538</v>
+        <v>621629</v>
       </c>
       <c r="R27" t="n">
-        <v>6896297</v>
+        <v>6896649</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3210,12 +3203,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3242,27 +3240,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130255328</v>
+        <v>130263782</v>
       </c>
       <c r="B28" t="n">
-        <v>5197</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3273,22 +3271,22 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vargberget, Vargberget, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>621778</v>
+        <v>621500</v>
       </c>
       <c r="R28" t="n">
-        <v>6896212</v>
+        <v>6896621</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3312,12 +3310,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3344,48 +3342,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130255532</v>
+        <v>130263783</v>
       </c>
       <c r="B29" t="n">
-        <v>91737</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vargberget, Vargberget, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>621763</v>
+        <v>621724</v>
       </c>
       <c r="R29" t="n">
-        <v>6896229</v>
+        <v>6896260</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3441,48 +3444,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130257300</v>
+        <v>130263784</v>
       </c>
       <c r="B30" t="n">
-        <v>91737</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vargberget, Vargberget, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>621622</v>
+        <v>621541</v>
       </c>
       <c r="R30" t="n">
-        <v>6896214</v>
+        <v>6896211</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3512,6 +3520,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3538,42 +3551,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130255293</v>
+        <v>130243698</v>
       </c>
       <c r="B31" t="n">
-        <v>79219</v>
+        <v>5179</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3582,10 +3591,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>621791</v>
+        <v>621551</v>
       </c>
       <c r="R31" t="n">
-        <v>6896209</v>
+        <v>6896636</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3612,12 +3621,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3644,53 +3653,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130263778</v>
+        <v>130255474</v>
       </c>
       <c r="B32" t="n">
-        <v>57864</v>
+        <v>5179</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Vargberget, Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>621592</v>
+        <v>621778</v>
       </c>
       <c r="R32" t="n">
-        <v>6896635</v>
+        <v>6896212</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3714,12 +3723,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3746,27 +3755,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130263780</v>
+        <v>130263830</v>
       </c>
       <c r="B33" t="n">
-        <v>57864</v>
+        <v>57132</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3774,25 +3783,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Vargberget, Vargberget, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>621666</v>
+        <v>621662</v>
       </c>
       <c r="R33" t="n">
-        <v>6896644</v>
+        <v>6896601</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3848,10 +3864,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130263783</v>
+        <v>130255089</v>
       </c>
       <c r="B34" t="n">
-        <v>57864</v>
+        <v>58114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3859,42 +3875,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Stamningsbäcken, Stamningsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>621724</v>
+        <v>621974</v>
       </c>
       <c r="R34" t="n">
-        <v>6896260</v>
+        <v>6896153</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3950,27 +3970,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130263784</v>
+        <v>130243894</v>
       </c>
       <c r="B35" t="n">
-        <v>57864</v>
+        <v>5199</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3979,24 +3999,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Vargberget, Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>621541</v>
+        <v>621536</v>
       </c>
       <c r="R35" t="n">
-        <v>6896211</v>
+        <v>6896570</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4020,17 +4035,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4057,27 +4067,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130263782</v>
+        <v>130255328</v>
       </c>
       <c r="B36" t="n">
-        <v>57864</v>
+        <v>5199</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4088,22 +4098,22 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Vargberget, Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>621500</v>
+        <v>621778</v>
       </c>
       <c r="R36" t="n">
-        <v>6896621</v>
+        <v>6896212</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4127,12 +4137,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4162,7 +4172,7 @@
         <v>130263779</v>
       </c>
       <c r="B37" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4274,53 +4284,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130263781</v>
+        <v>130255573</v>
       </c>
       <c r="B38" t="n">
-        <v>57864</v>
+        <v>106243</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Vargberget, Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>621629</v>
+        <v>621738</v>
       </c>
       <c r="R38" t="n">
-        <v>6896649</v>
+        <v>6896216</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4344,17 +4349,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4378,6 +4378,103 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130255731</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Vargberget, Vargberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>621752</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6896206</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61824-2025 artfynd.xlsx
+++ b/artfynd/A 61824-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130243835</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130243809</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256265</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256808</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263778</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263782</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263784</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130243698</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130243894</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1690,6 +1740,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263779</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1787,6 +1842,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255188</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255326</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1981,6 +2046,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130244332</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2078,6 +2148,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130244182</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2175,6 +2250,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130244293</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2272,6 +2352,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130244448</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2369,6 +2454,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255442</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2466,6 +2556,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257248</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2563,6 +2658,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257365</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2660,6 +2760,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256107</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2757,6 +2862,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130244132</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2854,6 +2964,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256142</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2960,6 +3075,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130243363</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3057,6 +3177,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130244467</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3154,6 +3279,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255559</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3251,6 +3381,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255532</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3348,6 +3483,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256102</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3445,6 +3585,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130257300</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3551,6 +3696,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255293</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3653,6 +3803,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263780</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3760,6 +3915,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263781</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3862,6 +4022,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263783</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3964,6 +4129,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255474</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4073,6 +4243,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263830</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4179,6 +4354,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255089</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4281,6 +4461,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255328</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4378,6 +4563,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255573</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4475,8 +4665,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255731</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>